--- a/output/full_scan/batch_seq1_2026-09-02.xlsx
+++ b/output/full_scan/batch_seq1_2026-09-02.xlsx
@@ -4937,7 +4937,7 @@
         <v/>
       </c>
       <c r="D85" s="2" t="n">
-        <v>255.1336452342042</v>
+        <v>255.1336452342041</v>
       </c>
       <c r="E85" s="2" t="n">
         <v>13.55</v>
